--- a/CoTCM/data/standard_set_50/standard_50_symptom_set.xlsx
+++ b/CoTCM/data/standard_set_50/standard_50_symptom_set.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="herb_molecule_prescription" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="herb_molecule_prescription" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="provenance" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -474,7 +475,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -505,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,7 +515,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
@@ -536,7 +537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -545,7 +546,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
@@ -567,7 +568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -576,7 +577,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>15</v>
@@ -598,7 +599,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -607,7 +608,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>11</v>
@@ -629,7 +630,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -638,7 +639,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
@@ -660,7 +661,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -669,7 +670,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>8</v>
@@ -691,7 +692,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -700,7 +701,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
@@ -722,7 +723,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -731,7 +732,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,7 +763,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>9</v>
@@ -784,7 +785,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -815,7 +816,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -846,7 +847,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -877,7 +878,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,7 +887,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
@@ -908,7 +909,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -939,7 +940,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,7 +949,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
@@ -970,7 +971,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -979,7 +980,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
@@ -1001,7 +1002,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1010,7 +1011,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
@@ -1032,7 +1033,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1041,7 +1042,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>12</v>
@@ -1063,7 +1064,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1094,7 +1095,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1103,7 +1104,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>9</v>
@@ -1125,7 +1126,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1134,7 +1135,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>9</v>
@@ -1156,7 +1157,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1165,7 +1166,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
         <v>11</v>
@@ -1187,7 +1188,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1196,7 +1197,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>9</v>
@@ -1218,7 +1219,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1249,7 +1250,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1280,7 +1281,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1289,7 +1290,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
         <v>11</v>
@@ -1311,7 +1312,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1320,7 +1321,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>9</v>
@@ -1342,7 +1343,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1351,7 +1352,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>9</v>
@@ -1373,7 +1374,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1382,7 +1383,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
@@ -1404,7 +1405,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,7 +1414,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>8</v>
@@ -1435,7 +1436,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1444,7 +1445,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
         <v>11</v>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1475,7 +1476,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
         <v>9</v>
@@ -1497,7 +1498,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1528,7 +1529,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1537,7 +1538,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>14</v>
@@ -1559,7 +1560,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1568,7 +1569,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
         <v>9</v>
@@ -1590,7 +1591,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1599,7 +1600,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>11</v>
@@ -1621,7 +1622,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1630,7 +1631,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
         <v>11</v>
@@ -1652,7 +1653,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1661,7 +1662,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
         <v>12</v>
@@ -1683,7 +1684,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1692,7 +1693,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
         <v>9</v>
@@ -1714,7 +1715,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1745,7 +1746,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1776,7 +1777,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1785,7 +1786,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>11</v>
@@ -1807,7 +1808,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1816,7 +1817,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>10</v>
@@ -1838,7 +1839,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1847,7 +1848,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>9</v>
@@ -1869,7 +1870,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1878,7 +1879,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>11</v>
@@ -1900,7 +1901,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1909,7 +1910,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
         <v>9</v>
@@ -1931,7 +1932,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1940,7 +1941,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
         <v>12</v>
@@ -1962,7 +1963,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1971,7 +1972,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
         <v>10</v>
@@ -1993,7 +1994,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2075,7 +2076,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2112,7 +2113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2149,7 +2150,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2186,7 +2187,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2223,7 +2224,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2260,7 +2261,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2297,7 +2298,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2334,7 +2335,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2371,7 +2372,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2408,7 +2409,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2445,7 +2446,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2482,7 +2483,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>口眼歪斜、语言謇涩、半身不遂、关节痹痛、手足不温</t>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2519,7 +2520,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2556,7 +2557,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2593,7 +2594,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2630,7 +2631,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2667,7 +2668,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2704,7 +2705,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2741,7 +2742,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2778,7 +2779,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2815,7 +2816,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2852,7 +2853,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2889,7 +2890,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>红色丘疹、脓水浸淫、夜间剧痒、心烦失眠、血虚</t>
+          <t>风邪引起的症状、瘙痒、多汗</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2926,7 +2927,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2963,7 +2964,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3000,7 +3001,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3037,7 +3038,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3074,7 +3075,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3111,7 +3112,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3148,7 +3149,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3185,7 +3186,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3222,7 +3223,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>心烦失眠、口燥咽干、面赤升火、遗精滑泄、腰膝酸软</t>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3259,7 +3260,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3296,7 +3297,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3333,7 +3334,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3370,7 +3371,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3407,7 +3408,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3444,7 +3445,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3481,7 +3482,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3518,7 +3519,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3555,7 +3556,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3592,7 +3593,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3629,7 +3630,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3666,7 +3667,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3703,7 +3704,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3740,7 +3741,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3777,7 +3778,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>舌强不语、足废不用、上热下寒、面赤如妆、足冷过膝</t>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3814,7 +3815,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3851,7 +3852,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3888,7 +3889,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3925,7 +3926,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3962,7 +3963,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3999,7 +4000,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4036,7 +4037,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4073,7 +4074,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4110,7 +4111,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4147,7 +4148,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4184,7 +4185,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>咳声粗重、痰黄黏稠、咽喉干痛、鼻息灼热、胸胁胀痛</t>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4221,7 +4222,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4258,7 +4259,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4295,7 +4296,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4332,7 +4333,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4369,7 +4370,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4406,7 +4407,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4443,7 +4444,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4480,7 +4481,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4517,7 +4518,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4554,7 +4555,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4591,7 +4592,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4628,7 +4629,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4665,7 +4666,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4702,7 +4703,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4739,7 +4740,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咳声重浊、痰黄稠黏、气息粗促、久咳声哑、舌红苔黄腻</t>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4776,7 +4777,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4813,7 +4814,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4850,7 +4851,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4887,7 +4888,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4924,7 +4925,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4961,7 +4962,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4998,7 +4999,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5035,7 +5036,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>眩晕如坐舟船、头痛昏蒙、恶心呕吐、胸膈痞闷、舌苔白腻水滑</t>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5072,7 +5073,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5109,7 +5110,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5146,7 +5147,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5183,7 +5184,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5220,7 +5221,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5257,7 +5258,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5294,7 +5295,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5331,7 +5332,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5368,7 +5369,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5405,7 +5406,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>经前少腹灼痛、得热反剧、经前乳胀、烦躁易怒、肝郁气滞</t>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5442,7 +5443,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5479,7 +5480,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5516,7 +5517,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5553,7 +5554,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5590,7 +5591,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5627,7 +5628,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5664,7 +5665,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5701,7 +5702,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5738,7 +5739,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>全身关节游走性疼痛、关节肿胀麻木、身体羸瘦、头晕气短、恶心欲吐</t>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5775,7 +5776,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5812,7 +5813,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5849,7 +5850,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5886,7 +5887,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5923,7 +5924,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5960,7 +5961,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5997,7 +5998,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6034,7 +6035,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6071,7 +6072,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>恶寒无汗、头身疼痛、咳喘痰多、喉中痰鸣、胸腹胀憋闷</t>
+          <t>呕吐、虚汗、气喘</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6108,7 +6109,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6145,7 +6146,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6182,7 +6183,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6219,7 +6220,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6256,7 +6257,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6293,7 +6294,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6330,7 +6331,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6367,7 +6368,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6404,7 +6405,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6441,7 +6442,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6478,7 +6479,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6515,7 +6516,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6552,7 +6553,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6589,7 +6590,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6626,7 +6627,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6663,7 +6664,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>食不知味、食后腹胀、口燥舌干、肢体困重、面色㿠白</t>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6700,7 +6701,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6737,7 +6738,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6774,7 +6775,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6811,7 +6812,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6848,7 +6849,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6885,7 +6886,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -6922,7 +6923,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6959,7 +6960,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -6996,7 +6997,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7033,7 +7034,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>色㿠白、大便溏薄、胁胀嗳气、舌淡胖有齿痕、脉弦缓无力</t>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7070,7 +7071,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7107,7 +7108,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7144,7 +7145,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7181,7 +7182,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7218,7 +7219,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7255,7 +7256,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7292,7 +7293,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7329,7 +7330,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7366,7 +7367,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7403,7 +7404,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7440,7 +7441,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7477,7 +7478,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>痛如锥刺、夜间加重、舌紫黯瘀斑、脉沉涩、久痛不愈</t>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7514,7 +7515,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7551,7 +7552,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7588,7 +7589,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7625,7 +7626,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7662,7 +7663,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7699,7 +7700,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7736,7 +7737,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7773,7 +7774,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7810,7 +7811,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7847,7 +7848,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>鼻塞涕多、外邪夹杂(或伴风寒、湿热）、肺虚、气短声低</t>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7884,7 +7885,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7921,7 +7922,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7958,7 +7959,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7995,7 +7996,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8032,7 +8033,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8069,7 +8070,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -8106,7 +8107,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -8143,7 +8144,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8180,7 +8181,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8217,7 +8218,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>腰以下肿甚、腹胀便溏、四肢不温、痰湿引起的症状、胸闷不适</t>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8254,7 +8255,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8291,7 +8292,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8328,7 +8329,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8365,7 +8366,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8402,7 +8403,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8439,7 +8440,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8476,7 +8477,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8513,7 +8514,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8550,7 +8551,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8587,7 +8588,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>牙龈肿烂出血、咽喉肿痛、身面发黄、小便黄赤、胸腹胀气短</t>
+          <t>高血脂、热毒引起的症状、发热</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8624,7 +8625,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8661,7 +8662,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8698,7 +8699,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8735,7 +8736,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8772,7 +8773,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8809,7 +8810,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8846,7 +8847,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8883,7 +8884,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8920,7 +8921,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8957,7 +8958,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8994,7 +8995,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9031,7 +9032,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9068,7 +9069,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9105,7 +9106,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9142,7 +9143,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9179,7 +9180,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>手足拘挛、关节僵硬、麻木刺痛、遇寒加重、风痹游走性疼痛</t>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9216,7 +9217,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -9253,7 +9254,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9290,7 +9291,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -9327,7 +9328,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9364,7 +9365,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -9401,7 +9402,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9438,7 +9439,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -9475,7 +9476,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9512,7 +9513,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9549,7 +9550,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -9586,7 +9587,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -9623,7 +9624,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9660,7 +9661,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9697,7 +9698,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9734,7 +9735,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9771,7 +9772,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>手足无力、舌强语謇、血虚风动、血弱筋急、风湿引起的痛症</t>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9808,7 +9809,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9845,7 +9846,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9882,7 +9883,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9919,7 +9920,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9956,7 +9957,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9993,7 +9994,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10030,7 +10031,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10067,7 +10068,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10104,7 +10105,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10141,7 +10142,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10178,7 +10179,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10215,7 +10216,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>痈疽已成(局部红肿热痛)、正虚毒恋、脾胃虚弱、元气不足、心悸不安</t>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10252,7 +10253,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10289,7 +10290,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10326,7 +10327,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10363,7 +10364,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10400,7 +10401,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -10437,7 +10438,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10474,7 +10475,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10511,7 +10512,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10548,7 +10549,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -10585,7 +10586,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -10622,7 +10623,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10659,7 +10660,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -10696,7 +10697,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>全头疼痛、风邪为患、气血失调、血虚、痛经</t>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -10733,7 +10734,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -10770,7 +10771,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -10807,7 +10808,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -10844,7 +10845,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -10881,7 +10882,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -10918,7 +10919,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10955,7 +10956,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -10992,7 +10993,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -11029,7 +11030,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>憎寒壮热、头目昏疼、脘腹胀、嗳腐食臭、呕恶痰多</t>
+          <t>眼睛湿润、脾虚、心悸不安</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11066,7 +11067,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -11103,7 +11104,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -11140,7 +11141,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -11177,7 +11178,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -11214,7 +11215,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -11251,7 +11252,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -11288,7 +11289,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11325,7 +11326,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -11362,7 +11363,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>心悸恐慌、四肢抽搐、昼凉夜热、干咳或无咳、舌绛少苔或干裂</t>
+          <t>肾阴虚、出血、干咳、阴虚</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -11399,7 +11400,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11436,7 +11437,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -11473,7 +11474,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -11510,7 +11511,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -11547,7 +11548,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -11584,7 +11585,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -11621,7 +11622,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -11658,7 +11659,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -11695,7 +11696,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -11732,7 +11733,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -11769,7 +11770,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>风痹（疼痛游走不定）、寒痹(冷痛剧烈、得温稍减)、湿痹(酸沉重着、阴雨天加重)</t>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -11806,7 +11807,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11843,7 +11844,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11880,7 +11881,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -11917,7 +11918,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -11954,7 +11955,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11991,7 +11992,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12028,7 +12029,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -12065,7 +12066,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12102,7 +12103,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>赤带带下色红质稠、口苦咽干、烦躁易怒、神疲乏力、舌红苔黄腻</t>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -12139,7 +12140,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -12176,7 +12177,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -12213,7 +12214,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -12250,7 +12251,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -12287,7 +12288,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -12324,7 +12325,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -12361,7 +12362,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -12398,7 +12399,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -12435,7 +12436,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -12472,7 +12473,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -12509,7 +12510,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -12546,7 +12547,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -12583,7 +12584,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>水疱簇集、色黄白、破溃渗液、疼痛剧烈、舌红苔黄腻</t>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -12620,7 +12621,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -12657,7 +12658,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -12694,7 +12695,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -12731,7 +12732,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -12768,7 +12769,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12805,7 +12806,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -12842,7 +12843,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12879,7 +12880,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -12916,7 +12917,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>胸膈满闷、呼吸急促、肺胃失和：喘咳、呕吐、咳嗽</t>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12953,7 +12954,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -12990,7 +12991,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -13027,7 +13028,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -13064,7 +13065,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -13101,7 +13102,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -13138,7 +13139,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -13175,7 +13176,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -13212,7 +13213,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -13249,7 +13250,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -13286,7 +13287,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -13323,7 +13324,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>痔核肿痛、便血血色鲜红、舌红苔黄腻、脉滑数、烦躁</t>
+          <t>脓肿、中焦胀满、肾精不足</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -13360,7 +13361,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -13397,7 +13398,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -13434,7 +13435,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -13471,7 +13472,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -13508,7 +13509,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -13545,7 +13546,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -13582,7 +13583,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -13619,7 +13620,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -13656,7 +13657,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>发热微恶寒、微呕、心下支结、四肢关节烦疼、风寒引起的不适</t>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -13693,7 +13694,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -13730,7 +13731,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -13767,7 +13768,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -13804,7 +13805,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -13841,7 +13842,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -13878,7 +13879,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -13915,7 +13916,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -13952,7 +13953,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -13989,7 +13990,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>咳嗽喘急、喉中痰鸣、痰多稀白、恶寒无汗、舌苔白滑</t>
+          <t>咳嗽、水肿、心悸不安</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -14026,7 +14027,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -14063,7 +14064,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -14100,7 +14101,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -14137,7 +14138,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -14174,7 +14175,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -14211,7 +14212,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -14248,7 +14249,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -14285,7 +14286,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -14322,7 +14323,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -14359,7 +14360,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>项背强急、汗出恶风、脉沉迟或伴轻微发热、舌淡红少津、热毒引起的症状</t>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -14396,7 +14397,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -14433,7 +14434,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -14470,7 +14471,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -14507,7 +14508,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -14544,7 +14545,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -14581,7 +14582,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -14618,7 +14619,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14655,7 +14656,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>咳吐大量清稀涎沫、咽干但不欲饮、畏寒肢冷、舌淡苔白滑、脾胃虚弱</t>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14692,7 +14693,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -14729,7 +14730,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14766,7 +14767,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -14803,7 +14804,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -14840,7 +14841,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14877,7 +14878,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -14914,7 +14915,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -14951,7 +14952,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -14988,7 +14989,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -15025,7 +15026,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -15062,7 +15063,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>呕吐泄泻、胸膈痞满、痰喘咳嗽、寒热交作、小便赤涩</t>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -15099,7 +15100,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -15136,7 +15137,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -15173,7 +15174,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -15210,7 +15211,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -15247,7 +15248,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -15284,7 +15285,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -15321,7 +15322,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -15358,7 +15359,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -15395,7 +15396,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>大便夹黏液脓血、排便后肛门坠胀感不减、胀痛或刺痛（便后暂缓）、肝气郁结、月经失调</t>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -15432,7 +15433,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -15469,7 +15470,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -15506,7 +15507,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -15543,7 +15544,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -15580,7 +15581,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -15617,7 +15618,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -15654,7 +15655,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -15691,7 +15692,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -15728,7 +15729,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -15765,7 +15766,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -15802,7 +15803,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -15839,7 +15840,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -15876,7 +15877,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -15913,7 +15914,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>头面焮红肿痛、咽喉肿痛、舌干口燥、初起憎寒壮热、呼吸急促</t>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -15950,7 +15951,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -15987,7 +15988,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -16024,7 +16025,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -16061,7 +16062,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -16098,7 +16099,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -16135,7 +16136,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -16172,7 +16173,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -16209,7 +16210,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -16246,7 +16247,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -16283,7 +16284,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -16320,7 +16321,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -16357,7 +16358,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -16394,7 +16395,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -16431,7 +16432,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>目赤肿痛：、畏光流泪、头痛鼻塞、眉骨酸胀、舌红苔薄黄</t>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -16468,7 +16469,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -16505,7 +16506,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -16542,7 +16543,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -16579,7 +16580,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -16616,7 +16617,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -16653,7 +16654,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -16690,7 +16691,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -16727,7 +16728,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -16764,7 +16765,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>耳下、颈侧肿块、低热或不热、舌暗或有瘀斑、脉弦涩</t>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -16801,7 +16802,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -16838,7 +16839,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -16875,7 +16876,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -16912,7 +16913,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -16949,7 +16950,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -16986,7 +16987,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17023,7 +17024,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -17060,7 +17061,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17097,7 +17098,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17134,7 +17135,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -17171,7 +17172,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>气血两虚、体型异常、脾肝不足、胎元不固、气虚引起的乏力</t>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -17208,7 +17209,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -17245,7 +17246,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17282,7 +17283,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -17319,7 +17320,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -17356,7 +17357,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -17393,7 +17394,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -17430,7 +17431,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -17467,7 +17468,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -17504,7 +17505,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -17541,7 +17542,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -17578,7 +17579,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>视物昏花、头晕目眩、五心烦热、血虚、月经失调</t>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17615,7 +17616,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -17652,7 +17653,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -17689,7 +17690,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -17726,7 +17727,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -17763,7 +17764,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -17800,7 +17801,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -17837,7 +17838,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -17874,7 +17875,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -17911,7 +17912,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -17948,7 +17949,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -17985,7 +17986,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -18022,7 +18023,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>眼部症状：眼睑红肿硬痛（眼胞红硬）、口干口臭、便秘尿黄、火热引起的烦躁、热毒引起的症状</t>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -18059,7 +18060,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -18096,7 +18097,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -18133,7 +18134,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18170,7 +18171,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -18207,7 +18208,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -18244,7 +18245,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -18281,7 +18282,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -18318,7 +18319,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18355,7 +18356,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>两胁胀闷疼痛、如弓弦紧绷、情绪抑郁加重、口苦咽干、肝血不足</t>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -18392,7 +18393,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -18429,7 +18430,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -18466,7 +18467,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -18503,7 +18504,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -18540,7 +18541,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -18577,7 +18578,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -18614,7 +18615,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -18651,7 +18652,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -18688,7 +18689,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>发热头痛、但不恶寒反口渴、春夏温病高发季、起病急骤、咽痛心烦</t>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -18725,7 +18726,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -18762,7 +18763,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -18799,7 +18800,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -18836,7 +18837,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -18873,7 +18874,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -18910,7 +18911,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -18947,7 +18948,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -18984,7 +18985,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -19021,7 +19022,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -19058,7 +19059,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -19095,7 +19096,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19132,7 +19133,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>急躁易怒、面红目赤、口苦咽干、头痛胁痛、或发疮疡</t>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19169,7 +19170,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19206,7 +19207,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19243,7 +19244,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19280,7 +19281,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19317,7 +19318,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -19354,7 +19355,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -19391,7 +19392,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -19428,7 +19429,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -19465,7 +19466,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -19502,7 +19503,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -19539,7 +19540,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>皮肤干燥脱屑、瘙痒无度、抓痕血痂、疹色偏红、遇热加重</t>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -19576,7 +19577,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -19613,7 +19614,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -19650,7 +19651,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -19687,7 +19688,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -19724,7 +19725,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -19761,7 +19762,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -19798,7 +19799,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -19835,7 +19836,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -19872,7 +19873,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -19909,7 +19910,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>瘙痒剧烈（夜甚）、抓痕血痂、皮肤干燥皲裂、心烦失眠、口干咽燥</t>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -19946,7 +19947,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -19983,7 +19984,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -20020,7 +20021,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -20057,7 +20058,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -20094,7 +20095,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -20131,7 +20132,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -20168,7 +20169,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -20205,7 +20206,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -20242,7 +20243,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>鼻部及周围皮肤潮红、毛细血管扩张、面部油腻、或见丘疹脓疱、口干口苦</t>
+          <t>呕吐、气滞引起的不适、便秘</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -20279,7 +20280,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -20316,7 +20317,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -20353,7 +20354,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -20390,7 +20391,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -20427,7 +20428,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -20464,7 +20465,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -20501,7 +20502,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -20538,7 +20539,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -20575,7 +20576,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -20612,7 +20613,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -20649,7 +20650,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>胃脘症状：灼痛拒按、呕酸苦水、胁气上逆、阵发燥热伴畏寒、心窝部烧灼感</t>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -20686,7 +20687,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -20723,7 +20724,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -20760,7 +20761,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -20797,7 +20798,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -20834,7 +20835,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -20871,7 +20872,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -20908,7 +20909,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -20945,7 +20946,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -20982,7 +20983,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>寒战高热交替、骨节灼痛拒按、关节肿胀烦疼、屈伸不利、面色萎黄晦暗</t>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21019,7 +21020,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21056,7 +21057,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -21093,7 +21094,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -21130,7 +21131,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -21167,7 +21168,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -21204,7 +21205,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -21241,7 +21242,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -21278,7 +21279,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -21315,7 +21316,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -21352,7 +21353,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -21389,7 +21390,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -21426,7 +21427,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>胁下、脘腹积块瘀滞、痛处固定不移、卧则腹内坠胀、久泻不止</t>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -21463,7 +21464,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -21500,7 +21501,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -21537,7 +21538,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -21574,7 +21575,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -21611,7 +21612,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -21648,7 +21649,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -21685,7 +21686,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -21722,7 +21723,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -21759,7 +21760,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -21796,7 +21797,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>咽喉肿痛、水呛、声嘶、咽部异物感、久病喑哑</t>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -21833,7 +21834,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -21870,7 +21871,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -21907,7 +21908,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -21944,7 +21945,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -21981,7 +21982,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -22018,7 +22019,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -22055,7 +22056,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -22092,7 +22093,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -22129,7 +22130,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -22166,7 +22167,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>突发或渐进性耳聋、伴腰膝酸软、耳鸣如蝉、眼珠刺痛、转动时加重</t>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -22193,6 +22194,2062 @@
         <is>
           <t>It has the effects of tonifying kidney yang, replenishing essence and blood, and moistening the intestines to relieve constipation.</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>reference_prescription</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>symptom_text_zh</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>selected_symptoms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>source_symptom_pool</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>source_column</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>disease_column_used</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>random_seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>小续命汤</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>便秘、口干舌燥、湿邪引起的症状、肺热引起的症状、阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>便秘 | 口干舌燥 | 湿邪引起的症状 | 肺热引起的症状 | 阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>感冒 | 肺热引起的咳嗽 | 水肿 | 风寒 | 元气不足 | 心慌心跳 | 心悸不安 | 口干舌燥 | 脾胃虚弱 | 湿热引起的症状 | 火毒引起的症状 | 出血 | 阳虚引起的症状 | 血瘀痛经 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛不适 | 肝气不舒 | 月经失调 | 多汗 | 血瘀引起的症状 | 气滞引起的不适 | 风寒引起的不适 | 咳嗽 | 哮喘 | 便秘 | 肺热引起的症状 | 肾阳虚引起的症状 | 寒湿引起的疼痛 | 湿邪引起的症状 | 痉挛 | 恶心呕吐</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>20260711</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>当归饮子</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>风邪引起的症状、瘙痒、多汗</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>风邪引起的症状 | 瘙痒 | 多汗</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>血虚 | 月经失调 | 疼痛 | 便秘 | 肝气不畅引起的疼痛 | 多汗 | 血瘀引起的症状 | 气滞引起的不适 | 风邪引起的症状 | 肾精不足 | 阴虚 | 肝气郁结 | 瘙痒 | 湿邪引起的症状 | 痉挛 | 风寒引起的不适 | 疹痒 | 出血 | 毒素引起的症状 | 肿痛 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛不适 | 恶心呕吐 | 水肿</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>20260712</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>清心莲子饮</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>脾气虚弱、脾胃虚弱、口干舌燥、出血</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>脾气虚弱 | 脾胃虚弱 | 口干舌燥 | 出血</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 火毒引起的症状 | 出血 | 阴虚 | 肺燥引起的咳嗽 | 血热引起的症状 | 肺热引起的咳嗽 | 虚热引起的不适 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛不适 | 脾虚引起的症状 | 肾虚引起的症状 | 心悸不安 | 精神不安 | 水肿 | 脾胃虚弱 | 元气不足 | 心慌心跳 | 口干舌燥 | 多汗 | 毒素引起的症状</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>20260713</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>地黄饮子</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>风邪引起的症状、寒湿引起的疼痛、肾阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>风邪引起的症状 | 寒湿引起的疼痛 | 肾阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>肾精不足 | 血虚 | 阴虚 | 肾阳虚引起的症状 | 筋骨无力 | 风邪引起的症状 | 肝肾不足引起的症状 | 遗精 | 腹泻 | 水肿 | 脾胃虚弱 | 心悸不安 | 胃虚引起的不适 | 口干舌燥 | 精血不足 | 便秘 | 脾胃虚寒 | 阳气不足 | 寒湿引起的疼痛 | 多汗 | 气虚 | 疼痛 | 经络不畅 | 肺燥引起的咳嗽 | 心火旺盛 | 湿邪引起的症状 | 痰瘀阻窍引起的症状 | 肿痛 | 神志不清 | 痰湿引起的症状 | 肿胀 | 风热引起的症状 | 头晕 | 视力模糊 | 疹出不畅 | 咳嗽多痰 | 恶心呕吐 | 风寒感冒 | 气血不足</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>20260714</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>清金化痰汤</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>肺燥引起的咳嗽、热盛引起的烦躁、脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>肺燥引起的咳嗽 | 热盛引起的烦躁 | 脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 出血 | 热盛引起的烦躁 | 小便不利 | 血液热毒引起的症状 | 咽喉疼痛 | 阴虚 | 肺燥引起的咳嗽 | 心火旺盛 | 肺热引起的咳嗽 | 水肿 | 呼吸不畅 | 痰湿引起的症状 | 气滞引起的不适 | 热毒引起的症状 | 口干舌燥 | 便秘 | 心血管疾病 | 寒湿引起的脾胃不适 | 脾胃虚弱 | 心悸不安 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛不适</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>20260715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>清肺汤</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>寒湿引起的脾胃不适、心悸不安、心火旺盛、便秘</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>寒湿引起的脾胃不适 | 心悸不安 | 心火旺盛 | 便秘</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 火毒引起的症状 | 出血 | 流产 | 肺热引起的咽喉疼痛 | 水肿 | 脾胃虚弱 | 心悸不安 | 痰湿引起的症状 | 寒湿引起的脾胃不适 | 痰湿引起的结节 | 气滞引起的不适 | 咳嗽多痰 | 肺热引起的症状 | 血虚 | 月经失调 | 疼痛 | 便秘 | 阴虚 | 心火旺盛 | 火热引起的烦躁 | 小便不利 | 血液热毒引起的症状 | 咳嗽 | 哮喘 | 肺燥引起的咳嗽 | 气虚引起的水肿 | 肾虚引起的头晕失眠 | 脾气虚弱 | 肌肉抽搐 | 药物相互作用 | 恶心呕吐 | 风寒感冒 | 寒湿引起的疼痛 | 气血不足 | 失眠不安 | 气血两虚症状</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>20260716</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>半夏白术天麻汤</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>寒湿引起的脾胃不适、水肿、恶心呕吐、脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>寒湿引起的脾胃不适 | 水肿 | 恶心呕吐 | 脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>呕吐 | 痰湿引起的结块 | 气滞引起的不适 | 肝阳上亢引起的症状 | 风寒引起的不适 | 水肿 | 脾胃虚弱 | 心悸不安 | 痰湿引起的症状 | 寒湿引起的脾胃不适 | 脾气虚弱 | 流产 | 咳嗽多痰 | 肌肉抽搐 | 疼痛 | 药物相互作用 | 恶心呕吐 | 风寒感冒 | 气血两虚</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>20260717</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>宣郁通经汤</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>痛经、咳嗽多痰、血瘀引起的症状、血热症状</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>痛经 | 咳嗽多痰 | 血瘀引起的症状 | 血热症状</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>肝郁气滞 | 痛经 | 多汗 | 血虚 | 月经失调 | 疼痛 | 便秘 | 热毒引起的症状 | 血瘀引起的症状 | 火热引起的烦躁 | 小便不利 | 血热症状 | 咳嗽多痰 | 炎症 | 细菌感染 | 脾气虚弱 | 肌肉抽搐 | 药物相互作用 | 发热 | 肝气不舒 | 阳气不足 | 流产 | 气滞血瘀 | 湿热 | 出血</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>20260718</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>桂枝芍药知母汤</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>风湿性疾病、痉挛、疼痛、多汗</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>风湿性疾病 | 痉挛 | 疼痛 | 多汗</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>风寒感冒 | 肢体麻木 | 阳气不足 | 肝郁气滞 | 月经失调 | 多汗 | 脾胃虚弱 | 热毒引起的症状 | 咳嗽多痰 | 肌肉抽搐 | 疼痛 | 肺热引起的咳嗽 | 水肿 | 恶心呕吐 | 易流产 | 口干舌燥 | 便秘 | 风湿性疾病 | 肢体疼痛 | 痉挛 | 内脏阳气不足 | 精神不安</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>20260719</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>厚朴麻黄汤</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>呕吐、虚汗、气喘</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>呕吐 | 虚汗 | 气喘</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>痰湿 | 胸腹胀 | 风寒感冒 | 哮喘 | 水肿 | 热毒引起的症状 | 肿胀 | 口干舌燥 | 咳嗽 | 气喘 | 便秘 | 呕吐 | 痞块 | 中焦寒湿 | 气虚 | 阳气不足 | 脾阳弱 | 关节疼痛 | 心悸不安 | 虚汗</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>20260720</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>升阳益胃汤</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>热毒引起的症状、痰湿、失眠不安、肝气不舒、发热</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>热毒引起的症状 | 痰湿 | 失眠不安 | 肝气不舒 | 发热</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>自汗 | 多汗 | 水肿 | 呕吐 | 胸腹胀 | 痞块 | 元气不足 | 脉弱 | 气虚咳嗽 | 心神不定 | 脾胃虚弱 | 热毒引起的症状 | 咳嗽多痰 | 肌肉抽搐 | 风寒感冒 | 风湿痹痛 | 痉挛 | 肝气不舒 | 痛经 | 寒冷引起的疼痛 | 肢体麻木 | 胃部不适 | 恶心呕吐 | 气滞引起的不适 | 痰湿 | 失眠不安 | 心悸不安 | 湿热 | 小便不利 | 发热 | 肝气郁结 | 阳虚引起的症状 | 习惯性流产 | 血液循环不畅</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>20260721</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>完带汤</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>黏膜损伤、湿热、多汗、疼痛、水肿</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>黏膜损伤 | 湿热 | 多汗 | 疼痛 | 水肿</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>脾胃虚弱 | 水肿 | 多汗 | 先兆流产 | 肺燥引起的症状 | 肾虚引起的症状 | 气虚 | 心悸不安 | 失眠不安 | 肝阳上亢引起的头痛 | 月经失调 | 血热引起的症状 | 湿热 | 湿气重引起的症状 | 风寒引起的不适 | 视力模糊 | 咳嗽多痰 | 肌肉抽搐 | 疼痛 | 呕吐 | 气机不畅引起的不适 | 湿痰引起的症状 | 溃疡出血 | 感染炎症 | 黏膜损伤 | 发热 | 肝郁气滞 | 阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>20260722</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>身痛逐瘀汤</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>肿胀、血虚引起的痛经、经闭、筋骨无力、血瘀引起的症状</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>肿胀 | 血虚引起的痛经 | 经闭 | 筋骨无力 | 血瘀引起的症状</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>风湿痹痛 | 血瘀引起的关节疼痛 | 血瘀引起的症状 | 脾胃虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛 | 寒湿引起的痛症 | 风寒引起的关节疼痛 | 肿胀 | 组织损伤 | 血虚引起的痛经 | 便秘 | 食积 | 出血 | 痛症 | 肝气郁结 | 先兆流产 | 月经失调 | 肝肾亏虚 | 筋骨无力 | 痛经 | 经闭 | 癫痫抽搐 | 热症引起的症状 | 风热引起的咳嗽 | 水肿 | 经络不畅</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>20260723</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>辛夷散</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>月经失调、鼻塞、脾肺虚弱、肝功能异常</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>月经失调 | 鼻塞 | 脾肺虚弱 | 肝功能异常</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>鼻塞 | 流涕 | 头痛 | 风寒感冒 | 咳嗽 | 痰多引起的症状 | 气喘 | 风寒引起的不适 | 关节疼痛 | 肌肉疼痛 | 疼痛 | 发热 | 肝功能异常 | 炎症 | 病毒感染 | 血瘀引起的症状 | 高血压引起的头痛 | 月经失调 | 痛经 | 湿热引起的症状 | 湿邪引起的症状 | 脾肺虚弱 | 咳嗽多痰 | 肌肉抽搐 | 肿胀</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>20260724</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>实脾散</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>湿邪引起的症状、经络不畅、湿热引起的症状、痰湿引起的症状、神经系统功能失调</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>湿邪引起的症状 | 经络不畅 | 湿热引起的症状 | 痰湿引起的症状 | 神经系统功能失调</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>痰湿引起的症状 | 胸闷不适 | 胃胀 | 脾胃虚弱 | 湿热引起的症状 | 多汗 | 先兆流产 | 肝郁气滞 | 湿邪引起的症状 | 气滞引起的不适 | 疟疾 | 腹胀 | 水肿 | 寒湿引起的疼痛 | 阳虚引起的症状 | 脾胃虚寒 | 心悸不安 | 神经系统功能失调 | 中焦寒湿 | 经络不畅 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>20260725</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>甘露饮</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>高血脂、热毒引起的症状、发热</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>高血脂 | 热毒引起的症状 | 发热</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>咳嗽 | 哮喘 | 糖尿病 | 炎症 | 肾虚引起的症状 | 气血不足 | 阴虚引起的干燥 | 肺燥引起的症状 | 心火旺盛 | 中焦胀满 | 消化不良 | 发热 | 高血压 | 高血脂 | 血液循环不畅 | 肿瘤 | 胃虚引起的不适 | 肺热引起的症状 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 疼痛 | 热毒引起的症状 | 出血 | 先兆流产</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>20260726</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>三痹汤</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>寒湿引起的疼痛、筋骨疼痛、肾虚引起的症状、脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>寒湿引起的疼痛 | 筋骨疼痛 | 肾虚引起的症状 | 脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>肝肾不足引起的症状 | 筋骨疼痛 | 月经失调 | 出血 | 先兆流产 | 感冒 | 风湿引起的痛症 | 寒湿引起的疼痛 | 疼痛 | 风寒引起的不适 | 痹症 | 元气不足 | 脉弱 | 脾肺虚弱 | 水肿 | 心悸不安 | 脾胃虚弱 | 血虚 | 痛经 | 便秘 | 肝郁气滞 | 多汗 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 风湿痹症 | 肾虚引起的症状 | 气血不足 | 血瘀引起的症状 | 风寒 | 关节疼痛 | 毒疮</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>20260727</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>大秦艽汤</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>脾气虚弱、风湿痛、肌肉疼痛</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>脾气虚弱 | 风湿痛 | 肌肉疼痛</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>风湿引起的痛症 | 关节疼痛 | 风湿痹症 | 筋骨疼痛 | 水肿 | 肾阳虚引起的症状 | 肌肉疼痛 | 阳虚引起的症状 | 寒湿引起的疼痛 | 脾胃虚弱 | 血瘀引起的症状 | 气滞引起的不适 | 风寒 | 血虚 | 痛经 | 便秘 | 咳嗽 | 痰湿引起的症状 | 风寒湿引起的疼痛 | 湿气重引起的症状 | 痉挛 | 热毒引起的症状 | 湿热引起的症状 | 出血 | 先兆流产 | 炎症 | 肿胀 | 口干舌燥 | 风湿痛 | 局部肿胀 | 脾气虚弱 | 多汗 | 肾虚引起的症状 | 气血不足 | 心悸不安</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>20260728</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>托里消毒散</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>湿热引起的症状、脾气虚弱、便秘、咳嗽多痰</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 脾气虚弱 | 便秘 | 咳嗽多痰</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>元气不足 | 心悸不安 | 失眠不安 | 脾胃虚弱 | 血瘀引起的症状 | 气滞 | 风寒 | 肝郁气滞 | 月经失调 | 多汗 | 血虚 | 痛经 | 便秘 | 疮毒 | 水肿 | 脾气虚弱 | 湿气重引起的症状 | 先兆流产 | 热毒引起的症状 | 风热引起的症状 | 局部肿胀 | 湿热引起的症状 | 咳嗽多痰 | 肌肉抽搐 | 消化不良 | 痈肿 | 蛆虫感染 | 咽喉疼痛 | 痰多引起的症状 | 肺部感染</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>20260729</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>清上蠲痛汤</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>先兆流产、风寒、风寒湿引起的疼痛、湿热引起的症状、痛经</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>先兆流产 | 风寒 | 风寒湿引起的疼痛 | 湿热引起的症状 | 痛经</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>血虚 | 痛经 | 便秘 | 血瘀引起的症状 | 气滞引起的不适 | 风寒 | 局部肿胀 | 痰湿引起的症状 | 风寒湿引起的疼痛 | 风湿引起的痛症 | 痉挛 | 热毒引起的症状 | 风热感冒 | 头痛 | 眼睛不适 | 脾虚 | 眼睛湿润 | 湿热引起的症状 | 出血 | 先兆流产 | 阴虚 | 干咳 | 心悸不安 | 脾气虚弱 | 咳嗽多痰 | 肌肉抽搐 | 消化不良</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>20260730</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>养胃汤</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>眼睛湿润、脾虚、心悸不安</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>眼睛湿润 | 脾虚 | 心悸不安</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>脾气虚弱 | 湿热引起的症状 | 咳嗽多痰 | 肌肉抽搐 | 消化不良 | 痰湿引起的胸闷不适 | 气胀 | 脾虚 | 眼睛湿润 | 呕吐 | 痰多引起的症状 | 腹胀 | 痰湿引起的症状 | 暑湿引起的不适 | 食欲不振 | 疟疾 | 水肿 | 脾胃虚弱 | 心悸不安 | 元气不足 | 失眠不安</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>20260731</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>S022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>三甲复脉汤</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>肾阴虚、出血、干咳、阴虚</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>肾阴虚 | 出血 | 干咳 | 阴虚</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>胃部不适 | 胃溃疡 | 免疫力低下 | 脾气虚弱 | 湿热引起的症状 | 咳嗽多痰 | 肌肉抽搐 | 消化不良 | 身体虚弱 | 精气不足 | 贫血 | 肝郁气滞 | 月经失调 | 多汗 | 阴虚 | 干咳 | 心悸不安 | 出血 | 干燥引起的不适 | 血虚 | 血瘀引起的症状 | 便秘 | 小便不利 | 痰多引起的症状 | 咽喉疼痛 | 肾阴虚 | 骨痛 | 心血不足引起的症状</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>20260732</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>蠲痹汤</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>肾阳虚引起的症状、经期不调、风寒、血虚</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>肾阳虚引起的症状 | 经期不调 | 风寒 | 血虚</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>寒冷引起的疼痛 | 风寒 | 风湿引起的关节疼痛 | 经络不畅 | 肾阳虚引起的症状 | 血瘀引起的症状 | 小便不利 | 血虚 | 经期不调 | 便秘 | 脾气虚弱 | 肌肉抽搐 | 气滞引起的不适 | 疼痛 | 肿胀 | 血液循环不畅 | 气机不畅引起的不适 | 消化不良</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>20260733</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>清肝止淋汤</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>月经失调、血虚、热毒引起的症状、血热引起的出血</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>月经失调 | 血虚 | 热毒引起的症状 | 血热引起的出血</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>肝气郁结 | 月经失调 | 多汗 | 血虚 | 便秘 | 肾精不足 | 阴虚 | 血热引起的出血 | 干燥引起的不适 | 热毒引起的症状 | 血瘀引起的症状 | 湿热引起的症状 | 疮疡肿痛 | 发热 | 肝肾不足引起的症状 | 筋骨无力 | 腹痛 | 流产 | 脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>20260734</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>除湿胃苓汤</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>湿气引起的皮疹、寒证引起的疼痛、暑热不适、水肿、湿气引起的脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>湿气引起的皮疹 | 寒证引起的疼痛 | 暑热不适 | 水肿 | 湿气引起的脾胃虚弱</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>湿气引起的脾胃虚弱 | 风寒引起的不适 | 视力模糊 | 腹胀 | 胃气失调引起的呕吐 | 气机不畅引起的不适 | 湿痰引起的症状 | 水肿 | 热毒引起的症状 | 脾气虚弱 | 湿气引起的多尿 | 多汗 | 暑热不适 | 湿气引起的皮疹 | 疮疡肿痛 | 外感风寒 | 湿气引起的肌痉挛 | 火热引起的烦躁 | 血瘀引起的症状 | 湿热引起的症状 | 肾阳虚引起的症状 | 寒证引起的疼痛 | 热毒引起的咳嗽 | 肌肉痉挛</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>20260735</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>清燥救肺汤</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>炎症引起的肿胀、高血糖、休克、口干舌燥、心火旺盛</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>炎症引起的肿胀 | 高血糖 | 休克 | 口干舌燥 | 心火旺盛</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>咳嗽 | 哮喘 | 高血糖 | 炎症 | 视力模糊 | 风热引起的症状 | 肺热引起的症状 | 火毒引起的症状 | 炎症引起的肿胀 | 口干舌燥 | 脾气虚弱 | 热毒引起的咳嗽 | 痉挛性疼痛 | 脉弱 | 休克 | 疲劳无力 | 便秘 | 血虚 | 风邪引起的症状 | 出血 | 干燥引起的不适 | 阴虚 | 肺气虚弱 | 肺燥引起的咳嗽 | 心火旺盛</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>20260736</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>凉血地黄汤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>脓肿、中焦胀满、肾精不足</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>脓肿 | 中焦胀满 | 肾精不足</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>烦躁 | 失眠不安 | 疼痛 | 发热 | 肝脏受损 | 免疫力低下 | 炎症 | 病毒感染 | 月经失调 | 血瘀引起的症状 | 便秘 | 肾精不足 | 血虚 | 阴虚 | 火毒引起的症状 | 湿热引起的症状 | 气机不畅引起的不适 | 中焦胀满 | 出血 | 流产 | 肿胀 | 伤口愈合缓慢 | 风寒引起的不适 | 瘙痒 | 脓肿 | 脾气虚弱 | 热毒引起的咳嗽 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>20260737</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>柴胡桂枝汤</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>失眠不安、气血不调、热毒引起的咳嗽</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>失眠不安 | 气血不调 | 热毒引起的咳嗽</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>风寒引起的不适 | 经络不畅 | 阳气不足 | 热毒引起的症状 | 湿热引起的症状 | 出血 | 流产 | 元气不足 | 脉弱 | 脾肺虚弱 | 口干舌燥 | 失眠不安 | 脾气虚弱 | 热毒引起的咳嗽 | 痉挛性疼痛 | 逆气引起的呕吐 | 湿痰积聚 | 积块瘀滞 | 疼痛 | 经血不调 | 多汗 | 脾胃虚弱 | 气血不调 | 痰多引起的咳嗽 | 发热 | 肝郁气滞</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>20260738</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>射干麻黄汤</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>咳嗽、水肿、心悸不安</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>咳嗽 | 水肿 | 心悸不安</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>热毒引起的症状 | 痰多引起的症状 | 咽喉疼痛 | 风寒引起的发热 | 咳嗽 | 水肿 | 痰湿引起的症状 | 呕吐 | 恶寒 | 风寒引起的头痛 | 关节疼痛 | 干咳无痰 | 多汗 | 心悸不安 | 气虚 | 脾胃虚弱 | 气血不足 | 疼痛 | 肿块</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>20260739</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>温脾丸</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>乳汁过多、热毒引起的便秘、阳气不足</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>乳汁过多 | 热毒引起的便秘 | 阳气不足</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>热毒引起的症状 | 湿气重引起的症状 | 骨蒸发热 | 痈肿疼痛 | 消化不良 | 乳汁过多 | 寒证引起的疼痛 | 呕吐 | 腹泻 | 阳虚引起的症状 | 经络不畅 | 脾胃虚寒 | 肺寒引起的咳嗽 | 阳气不足 | 寒湿引起的郁痛 | 肾阳虚引起的症状 | 寒湿引起的疼痛 | 血虚 | 痛经 | 便秘 | 热毒引起的便秘 | 月经失调 | 湿热引起的症状</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>20260740</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>延年薯蓣酒</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>湿邪引起的症状、湿气重引起的症状、肺燥引起的咳嗽</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>湿邪引起的症状 | 湿气重引起的症状 | 肺燥引起的咳嗽</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>脾胃虚弱 | 肺燥引起的咳嗽 | 肾虚引起的症状 | 脾虚引起的消化不良 | 湿气重引起的症状 | 多汗 | 尿频尿急 | 心悸不安 | 瘀血引起的疼痛 | 月经失调 | 烦躁 | 外感风寒 | 湿邪引起的症状 | 肝肾不足引起的症状 | 遗精 | 元气不足 | 脉弱 | 肺燥引起的症状 | 痰湿引起的症状 | 呕吐</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>20260741</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>六和汤</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>气喘、脉弱、积块瘀滞、痰湿引起的症状</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>气喘 | 脉弱 | 积块瘀滞 | 痰湿引起的症状</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 胸腹胀 | 消化不良 | 湿气引起的食欲不振 | 脾胃虚寒 | 呕吐 | 痰湿引起的症状 | 积块瘀滞 | 咳嗽 | 气喘 | 便秘 | 元气不足 | 脉弱 | 肺燥引起的症状 | 心悸不安 | 脾虚引起的消化不良 | 热毒引起的症状 | 痉挛性疼痛 | 尿量少 | 水肿 | 脾胃虚弱 | 湿浊引起的不适 | 胃寒引起的呕吐 | 肝气不舒 | 脾胃功能失调</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>20260742</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>芍药汤</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>疟疾、肝气郁结、湿热引起的症状、痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>疟疾 | 肝气郁结 | 湿热引起的症状 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>肝气郁结 | 月经失调 | 多汗 | 血虚 | 经络不畅 | 疼痛 | 便秘 | 湿热引起的症状 | 炎症 | 肿胀 | 消化不良 | 腹胀 | 疟疾 | 气滞引起的不适 | 脾虚引起的消化不良 | 热毒引起的症状 | 痰湿引起的症状 | 痉挛性疼痛 | 热毒引起的便秘 | 血热引起的症状 | 出血 | 习惯性流产 | 寒湿引起的疼痛 | 风寒引起的不适 | 阳气不足</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>20260743</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>普济消毒饮子</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>脾胃虚弱、热邪引起的症状、脉弱、脏腑功能失调、咽喉肿结</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>脾胃虚弱 | 热邪引起的症状 | 脉弱 | 脏腑功能失调 | 咽喉肿结</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>湿热引起的症状 | 热毒引起的症状 | 出血 | 习惯性流产 | 元气不足 | 脉弱 | 脾胃虚弱 | 肺燥引起的症状 | 心悸不安 | 痰湿引起的症状 | 中焦胀满 | 寒证引起的疼痛 | 气滞引起的不适 | 血热引起的症状 | 阴虚 | 脾虚引起的消化不良 | 痉挛性疼痛 | 热毒引起的肿胀 | 结节 | 肿胀 | 风热引起的症状 | 咽喉疼痛 | 肺热引起的症状 | 咽喉肿结 | 失眠不安 | 疼痛 | 发热 | 肝脏受损 | 免疫力低下 | 炎症 | 病毒感染 | 热邪引起的症状 | 脏腑功能失调 | 阳虚引起的症状 | 痰液过多 | 肺脓肿</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>20260744</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>羌活胜风汤</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>脾虚引起的消化不良、疼痛、目赤、湿邪引起的症状</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>脾虚引起的消化不良 | 疼痛 | 目赤 | 湿邪引起的症状</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>脾虚引起的消化不良 | 湿热引起的症状 | 多汗 | 习惯性流产 | 中焦胀满 | 气滞引起的不适 | 消化不良 | 寒湿引起的疼痛 | 风寒引起的不适 | 疼痛 | 血瘀引起的症状 | 风湿引起的痛症 | 痛经 | 肿胀 | 肺脓肿 | 关节疼痛 | 经络不畅 | 湿邪引起的症状 | 痉挛 | 风热引起的症状 | 气逆引起的咳嗽 | 痰多引起的症状 | 肺热引起的症状 | 咽喉疼痛 | 痰液过多 | 风热引起的头痛 | 目赤 | 皮肤瘙痒 | 出血 | 热毒引起的症状 | 痰湿引起的症状 | 痉挛性疼痛 | 热邪引起的症状 | 肝郁气滞 | 脾胃功能失调 | 阳虚引起的症状 | 热毒引起的出血</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>20260745</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>牛蒡甘桔汤</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>痉挛性疼痛、咽喉疼痛、热毒引起的症状、肿胀</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>痉挛性疼痛 | 咽喉疼痛 | 热毒引起的症状 | 肿胀</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>肿胀 | 疼痛 | 咽喉疼痛 | 肺热引起的症状 | 痰液过多 | 肺脓肿 | 胃气上逆引起的呕吐 | 气滞引起的不适 | 热毒引起的肿胀 | 痰湿引起的症状 | 肿痛 | 湿热引起的症状 | 火毒引起的症状 | 毒素引起的症状 | 血瘀引起的症状 | 风湿引起的痛症 | 热毒引起的症状 | 脾虚引起的消化不良 | 痉挛性疼痛 | 血瘀引起的肿胀</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>20260746</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>泰山磐石散</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>经络不畅、血虚、气虚引起的乏力</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>经络不畅 | 血虚 | 气虚引起的乏力</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>气虚引起的乏力 | 脉弱 | 脾肺功能不足 | 水肿 | 失眠不安 | 表虚自汗 | 血虚 | 月经失调 | 疼痛 | 便秘 | 血虚引起的出血 | 肝肾不足引起的症状 | 经络不畅 | 热毒引起的症状 | 湿热引起的症状 | 出血 | 习惯性流产 | 血瘀引起的症状 | 气滞引起的不适 | 风邪引起的症状 | 关节疼痛 | 肝郁气滞 | 血虚引起的月经失调 | 多汗 | 精血不足 | 阴虚 | 脾虚引起的消化不良 | 湿气重引起的症状 | 痰湿引起的症状 | 痉挛性疼痛 | 腹泻</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>20260747</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>滋阴降火汤</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>血虚、阳虚引起的症状、疼痛、习惯性流产</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>血虚 | 阳虚引起的症状 | 疼痛 | 习惯性流产</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>血虚 | 月经失调 | 疼痛 | 便秘 | 血瘀引起的症状 | 气滞引起的不适 | 风邪引起的症状 | 关节疼痛 | 精血不足 | 阴虚 | 热毒引起的症状 | 湿热引起的症状 | 疮毒 | 肺燥引起的症状 | 燥热引起的症状 | 肝郁气滞 | 血虚引起的月经失调 | 多汗 | 出血 | 习惯性流产 | 发热 | 阳虚引起的症状 | 脾虚引起的消化不良 | 痰湿引起的症状 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>20260748</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>清胃汤</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>口干舌燥、干燥引起的不适、疼痛、湿痰引起的症状</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>口干舌燥 | 干燥引起的不适 | 疼痛 | 湿痰引起的症状</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>火热引起的烦躁 | 热毒引起的症状 | 小便不利 | 气滞引起的不适 | 咳嗽 | 炎症 | 干燥引起的不适 | 口干舌燥 | 湿热引起的症状 | 胃失和降引起的呕吐 | 气机不畅引起的不适· | 湿痰引起的症状 | 热毒引起的肿胀 | 结节 | 血虚 | 月经失调 | 疼痛 | 便秘 | 风寒引起的不适 | 疹痒 | 出血 | 习惯性流产 | 外感风寒 | 风湿引起的痛症 | 痉挛 | 脾胃虚弱 | 痰湿引起的症状 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>20260749</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>解郁汤</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>元气不足、腹泻、气滞引起的不适、头目不适</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>元气不足 | 腹泻 | 气滞引起的不适 | 头目不适</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>元气不足 | 脉弱 | 脾肺虚弱 | 干燥引起的不适 | 心悸不安 | 脾胃虚弱 | 湿气重引起的症状 | 多汗 | 习惯性流产 | 脾胃功能失调 | 血虚 | 月经失调 | 疼痛 | 便秘 | 肝郁气滞 | 血虚引起的月经失调 | 气滞引起的不适 | 腹泻 | 火热引起的烦躁 | 热毒引起的症状 | 小便不利 | 血热引起的症状 | 风热引起的症状 | 头目不适 | 疹出不畅</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>20260750</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>柴葛解肌汤</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>血热引起的症状、阴虚、湿热引起的症状、脾胃虚弱、痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>血热引起的症状 | 阴虚 | 湿热引起的症状 | 脾胃虚弱 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>发热 | 肝气不疏引起的症状 | 阳气下陷引起的症状 | 腹泻 | 气虚 | 津液不足 | 疹出不畅 | 血瘀引起的症状 | 热毒引起的症状 | 血热引起的症状 | 脾胃虚弱 | 痰湿引起的症状 | 痉挛性疼痛 | 湿热引起的症状 | 出血 | 习惯性流产 | 热痰引起的症状 | 气滞引起的不适 | 精血不足 | 阴虚</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>20260751</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>S042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>柴胡清肝汤</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>尿量少、血瘀引起的症状、发热、风邪引起的症状、月经失调</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>尿量少 | 血瘀引起的症状 | 发热 | 风邪引起的症状 | 月经失调</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>发热 | 肝气不舒 | 阳气下陷引起的症状 | 精血不足 | 阴虚 | 血虚 | 月经失调 | 疼痛 | 便秘 | 血瘀引起的症状 | 热毒引起的症状 | 血热引起的症状 | 肿胀 | 结节 | 气滞引起的不适 | 风寒引起的不适 | 疹出不畅 | 风邪引起的症状 | 热毒引起的炎症 | 湿热引起的症状 | 出血 | 习惯性流产 | 热火旺盛引起的烦躁 | 尿量少 | 津液不足 | 水肿 | 脾胃虚弱 | 咳嗽 | 痉挛性疼痛 | 外感风寒 | 痉挛</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>20260752</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>S043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>四物消风饮</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>热毒引起的症状、血虚、风邪引起的症状</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>热毒引起的症状 | 血虚 | 风邪引起的症状</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>精血不足 | 阴虚 | 血虚 | 月经失调 | 疼痛 | 便秘 | 疹痒 | 出血 | 外感风寒 | 痉挛 | 血瘀引起的症状 | 热毒引起的症状 | 血热引起的症状 | 气滞引起的不适 | 风邪引起的症状 | 湿热引起的症状 | 目疾 | 翳障 | 风热引起的症状 | 眼疾 | 风湿引起的痛症 | 气滞血瘀 | 发热 | 肝气不舒 | 阳气下陷引起的症状</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>20260753</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>地黄饮</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>热毒引起的症状、便秘、痉挛性疼痛、风热引起的痉挛</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>热毒引起的症状 | 便秘 | 痉挛性疼痛 | 风热引起的痉挛</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>精血不足 | 阴虚 | 肿胀 | 疼痛 | 便秘 | 血虚 | 月经失调 | 热毒引起的症状 | 血瘀引起的症状 | 血热引起的症状 | 内外火热 | 肝郁气滞 | 眼疾 | 瘙痒 | 风热引起的痉挛 | 脾胃虚弱 | 湿热引起的症状 | 咳嗽 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>20260754</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>S045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>凉血四物汤</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>呕吐、气滞引起的不适、便秘</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>呕吐 | 气滞引起的不适 | 便秘</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>血虚 | 月经失调 | 疼痛 | 便秘 | 精血不足 | 阴虚 | 血瘀引起的症状 | 气滞引起的不适 | 风邪引起的症状 | 血热引起的症状 | 湿热引起的症状 | 火毒引起的症状 | 出血 | 习惯性流产 | 水肿 | 胃部不适 | 呕吐 | 痰湿引起的症状 | 脾胃虚弱 | 咳嗽 | 痉挛性疼痛</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>20260755</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>S046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>滋水清肝饮</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>胃部不适、肝气不舒、血热引起的症状</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>胃部不适 | 肝气不舒 | 血热引起的症状</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>精血不足 | 阴虚 | 血虚 | 月经失调 | 疼痛 | 便秘 | 肝阳上亢引起的头痛 | 多汗 | 肝肾不足引起的症状 | 失眠不安 | 神经衰弱 | 肝肾两虚 | 水肿 | 胃部不适 | 脾胃虚弱 | 胃虚引起的不适 | 肺虚引起的症状 | 肾虚引起的症状 | 发热 | 肝气不舒 | 阳气下陷引起的症状 | 热毒引起的不适 | 血热引起的症状 | 血瘀引起的症状 | 湿热引起的症状 | 尿路不畅</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>20260756</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>S047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>宣痹汤</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>热毒引起的烦躁、咳嗽、胃气上逆引起的呕吐、风湿引起的痛症</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>热毒引起的烦躁 | 咳嗽 | 胃气上逆引起的呕吐 | 风湿引起的痛症</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>风湿引起的痛症 | 水肿 | 疼痛 | 咳嗽 | 哮喘 | 便秘 | 肺热引起的症状 | 暑热不适 | 湿疹 | 伤口愈合缓慢 | 炎症 | 热毒引起的烦躁 | 血热引起的症状 | 脾胃虚弱 | 肌肉麻痹 | 脓肿 | 胃气上逆引起的呕吐 | 湿痰引起的症状 | 肿块 | 胃部不适 | 血瘀引起的症状 | 湿热引起的症状 | 黄疸</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>20260757</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>S048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>膈下逐瘀汤</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>消化不良、血瘀引起的出血、咳嗽、风寒引起的头痛</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>消化不良 | 血瘀引起的出血 | 咳嗽 | 风寒引起的头痛</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>血瘀引起的症状 | 消化不良 | 血瘀引起的出血 | 火毒引起的症状 | 便秘 | 气滞引起的不适 | 风寒引起的头痛 | 肌肉疼痛 | 热毒引起的症状 | 发热 | 肾阳虚引起的症状 | 脾胃虚弱 | 咳嗽 | 痉挛性疼痛 | 痛经 | 肝气郁结 | 月经失调</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>20260758</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>S049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>会厌逐瘀汤</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>精气不足、火毒感染、咳嗽、喉咙疼痛</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>精气不足 | 火毒感染 | 咳嗽 | 喉咙疼痛</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>血瘀引起的症状 | 便秘 | 痛经 | 脾胃虚弱 | 热毒引起的症状 | 咳嗽 | 痉挛性疼痛 | 喉咙疼痛 | 痰多引起的症状 | 肺脓肿 | 精气不足 | 骨髓虚损 | 血虚 | 阴虚 | 气滞引起的不适 | 血热引起的症状 | 火毒感染 | 发热 | 肝气郁结 | 阳虚引起的症状 | 消化不良</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>20260759</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>S050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>补肾活血汤</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>筋骨疼痛、血虚、便秘、遗精、血瘀引起的症状</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>筋骨疼痛 | 血虚 | 便秘 | 遗精 | 血瘀引起的症状</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>精髓亏损 | 血虚 | 阴虚 | 肝肾不足引起的症状 | 筋骨疼痛 | 流产 | 肾阴虚 | 肺燥引起的症状 | 腹泻 | 遗精 | 肝虚引起的视力模糊 | 便秘 | 血瘀引起的肿胀 | 组织损伤 | 血瘀引起的症状 | 风湿引起的关节疼痛 | 肢体麻木 | 风寒引起的不适 | 肾阳虚引起的症状</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>20260760</v>
       </c>
     </row>
   </sheetData>
